--- a/hw1/Use_case_descriptions/C111030.xlsx
+++ b/hw1/Use_case_descriptions/C111030.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\OneDrive\Desktop\소공\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscar/Desktop/4th_grade/1st/Software_Engineering/hw/hw1/Use_case_descriptions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1DB6AE5-9AB5-434C-A241-06B6B4993E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85600850-4649-364F-A743-705A88DA559D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2F6E1894-1E13-4ED7-A12D-A34235E4ED08}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{2F6E1894-1E13-4ED7-A12D-A34235E4ED08}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,45 +39,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>No.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Requirement</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Use Case(s)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>설문 등록</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>설문 조회/삭제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>설문 검색</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>특정 설문의 상세 내용 조회 및 삭제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>설문 제목, 설명, 문항, 응답 항목, 시작 시각 및 마감 시각 입력</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>설문 진행 상태 선택 및 키워드 입력</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Requirement List</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -194,7 +158,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,7 +277,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -335,9 +299,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -353,10 +314,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -693,253 +651,197 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFAF8D5E-662B-45C9-986E-8317241416BC}">
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="7.125" customWidth="1"/>
-    <col min="2" max="2" width="52.375" customWidth="1"/>
-    <col min="3" max="3" width="13.25" customWidth="1"/>
-    <col min="4" max="4" width="5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="54.125" customWidth="1"/>
-    <col min="6" max="6" width="38.5" customWidth="1"/>
+    <col min="1" max="1" width="5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="54.1640625" customWidth="1"/>
+    <col min="3" max="3" width="38.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:3" ht="19.5" customHeight="1">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+      <c r="C2" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="6">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="C3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>5</v>
-      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="6"/>
       <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7" t="s">
+      <c r="C4" s="7"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="6"/>
+      <c r="C5" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="6"/>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="7"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="6"/>
+      <c r="C7" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="6"/>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="7"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="6"/>
+      <c r="C10" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="6"/>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="7"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="6"/>
+      <c r="C12" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="6"/>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="7"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="6"/>
+      <c r="C14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="8"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="6"/>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="7"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="9"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="6">
+        <v>5</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="6"/>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="7"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="6"/>
+      <c r="C19" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="7"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="6"/>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="7"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="6"/>
+      <c r="C22" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D6" s="6"/>
-      <c r="E6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="D8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D11" s="6"/>
-      <c r="E11" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="8"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8" t="s">
+      <c r="B23" s="4"/>
+      <c r="C23" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D13" s="6"/>
-      <c r="E13" s="7" t="s">
+    <row r="24" spans="1:3" ht="36">
+      <c r="A24" s="6"/>
+      <c r="B24" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D15" s="6"/>
-      <c r="E15" s="7" t="s">
+      <c r="C24" s="7"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="6"/>
+      <c r="C25" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="6"/>
+      <c r="B26" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D16" s="10"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D17" s="6">
-        <v>5</v>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="8" t="s">
+      <c r="C26" s="7"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="9"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="11" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D18" s="6"/>
-      <c r="E18" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="8"/>
-    </row>
-    <row r="19" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D19" s="6"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D20" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="8"/>
-    </row>
-    <row r="21" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D21" s="6"/>
-      <c r="E21" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="8"/>
-    </row>
-    <row r="22" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D22" s="6"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D23" s="3">
-        <v>6</v>
-      </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="4:6" ht="33" x14ac:dyDescent="0.3">
-      <c r="D24" s="6"/>
-      <c r="E24" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="8"/>
-    </row>
-    <row r="25" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D25" s="6"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D26" s="6"/>
-      <c r="E26" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F26" s="8"/>
-    </row>
-    <row r="27" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D27" s="10"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="12" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
